--- a/data/ContentLists/content_list_complete_ACCEL_0718_DE_v3.xlsx
+++ b/data/ContentLists/content_list_complete_ACCEL_0718_DE_v3.xlsx
@@ -1,22 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/481a4202055a9895/Kurse/COMCAVE/COMCAVE - 2026KW28 - FSM 2/Teilnehmer/python_cc_fsm2_kw28_etl/data/ContentLists/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_49263CFB5B1423F2851A77138EBCADD091F55E27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8897E2A-1164-49CB-A003-C64B3410A43A}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView minimized="1" xWindow="31380" yWindow="1470" windowWidth="21240" windowHeight="16005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="content" sheetId="1" r:id="rId4"/>
-    <sheet name="specifications" sheetId="2" r:id="rId5"/>
+    <sheet name="content" sheetId="1" r:id="rId1"/>
+    <sheet name="specifications" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="61">
   <si>
     <t>ItemNumber</t>
   </si>
@@ -204,14 +209,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -238,13 +238,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -534,14 +542,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="31.140625" customWidth="1"/>
+    <col min="8" max="8" width="37.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -588,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -620,7 +635,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -653,21 +668,17 @@
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +689,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -689,7 +700,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -700,7 +711,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -711,7 +722,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -722,7 +733,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -733,7 +744,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -744,7 +755,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -755,7 +766,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -766,7 +777,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -777,7 +788,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -788,7 +799,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -799,7 +810,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -810,7 +821,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -821,7 +832,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -832,7 +843,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -843,7 +854,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -854,7 +865,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -866,8 +877,6 @@
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
--- a/data/ContentLists/content_list_complete_ACCEL_0718_DE_v3.xlsx
+++ b/data/ContentLists/content_list_complete_ACCEL_0718_DE_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/481a4202055a9895/Kurse/COMCAVE/COMCAVE - 2026KW28 - FSM 2/Teilnehmer/python_cc_fsm2_kw28_etl/data/ContentLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_49263CFB5B1423F2851A77138EBCADD091F55E27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8897E2A-1164-49CB-A003-C64B3410A43A}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_49263CFB5B1423F2851A77138EBCADD091F55E27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{118D6DC3-4352-4C08-A4F8-A9F73E76EBF7}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="31380" yWindow="1470" windowWidth="21240" windowHeight="16005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="31380" yWindow="195" windowWidth="21240" windowHeight="16005" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="content" sheetId="1" r:id="rId1"/>
@@ -677,6 +677,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
